--- a/artfynd/A 52563-2024 artfynd.xlsx
+++ b/artfynd/A 52563-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>110679672</v>
       </c>
       <c r="B2" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517880.50144161</v>
+        <v>517881</v>
       </c>
       <c r="R2" t="n">
-        <v>7132328.953234959</v>
+        <v>7132329</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-07-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>110679676</v>
       </c>
       <c r="B3" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517854.4066551963</v>
+        <v>517854</v>
       </c>
       <c r="R3" t="n">
-        <v>7131959.990495909</v>
+        <v>7131960</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2023-07-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110679673</v>
+        <v>110679678</v>
       </c>
       <c r="B4" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518037.1787008898</v>
+        <v>517982</v>
       </c>
       <c r="R4" t="n">
-        <v>7132132.017546716</v>
+        <v>7132007</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2023-07-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110679669</v>
+        <v>110679674</v>
       </c>
       <c r="B5" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,38 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517529</v>
+        <v>518037</v>
       </c>
       <c r="R5" t="n">
-        <v>7132628</v>
+        <v>7132132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110679678</v>
+        <v>110679673</v>
       </c>
       <c r="B6" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517981.8626988783</v>
+        <v>518037</v>
       </c>
       <c r="R6" t="n">
-        <v>7132007.596380278</v>
+        <v>7132132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,19 +1131,9 @@
           <t>2023-07-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110679679</v>
+        <v>110679675</v>
       </c>
       <c r="B7" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517981.8626988783</v>
+        <v>517854</v>
       </c>
       <c r="R7" t="n">
-        <v>7132007.596380278</v>
+        <v>7131960</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,19 +1228,9 @@
           <t>2023-07-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,50 +1257,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110679675</v>
+        <v>110679669</v>
       </c>
       <c r="B8" t="n">
-        <v>78612</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517854.4066551963</v>
+        <v>517529</v>
       </c>
       <c r="R8" t="n">
-        <v>7131959.990495909</v>
+        <v>7132628</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,19 +1329,9 @@
           <t>2023-07-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-07-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,118 +1355,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>110679674</v>
-      </c>
-      <c r="B9" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Storflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>518037.1787008898</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7132132.017546716</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-07-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-07-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52563-2024 artfynd.xlsx
+++ b/artfynd/A 52563-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110679672</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110679676</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110679678</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110679674</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110679673</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110679675</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,8 +1390,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110679669</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>